--- a/DJF/FTs/UAH_ASW SVT_TestProcedures.xlsx
+++ b/DJF/FTs/UAH_ASW SVT_TestProcedures.xlsx
@@ -23,12 +23,11 @@
     <sheet name="FT_UAH_ASW_SERV_128-0200" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="137">
   <si>
     <t>Doc. No.:</t>
   </si>
@@ -464,6 +463,9 @@
       </rPr>
       <t>TODO</t>
     </r>
+  </si>
+  <si>
+    <t>PMONID=0, PID=15, value=5, limit=1, prev status Unchecked, current status Within Limits</t>
   </si>
 </sst>
 </file>
@@ -843,7 +845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1045,6 +1047,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9790,12 +9793,16 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="12.75" customHeight="1">
+    <row r="45" spans="1:5" ht="76.2" customHeight="1">
       <c r="A45" s="72"/>
       <c r="B45" s="108"/>
       <c r="C45" s="85"/>
-      <c r="D45" s="85"/>
-      <c r="E45" s="75"/>
+      <c r="D45" s="109" t="s">
+        <v>129</v>
+      </c>
+      <c r="E45" s="97" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="46" spans="1:5" ht="12.75" customHeight="1">
       <c r="A46" s="86" t="s">

--- a/DJF/FTs/UAH_ASW SVT_TestProcedures.xlsx
+++ b/DJF/FTs/UAH_ASW SVT_TestProcedures.xlsx
@@ -413,9 +413,6 @@
     <t>PMONID = 0</t>
   </si>
   <si>
-    <t>Check that the TC[12,1] is accepted, started and completed successfully</t>
-  </si>
-  <si>
     <t>T0 + 40</t>
   </si>
   <si>
@@ -466,6 +463,9 @@
   </si>
   <si>
     <t>PMONID=0, PID=15, value=5, limit=1, prev status Unchecked, current status Within Limits</t>
+  </si>
+  <si>
+    <t>Check that the TC[12,1] is accepted, started and completed successfully, and that the monitor produces its first TM[12,12] with the transition Unchecked → Within Limits, confirming that the monitoring is active and PID 15 is within the configured range</t>
   </si>
 </sst>
 </file>
@@ -1026,6 +1026,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1047,7 +1048,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3536,7 +3536,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="99" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -3547,7 +3547,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="B11" s="99"/>
+      <c r="B11" s="100"/>
       <c r="D11" s="25" t="s">
         <v>43</v>
       </c>
@@ -3556,7 +3556,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B12" s="99"/>
+      <c r="B12" s="100"/>
       <c r="D12" s="33" t="s">
         <v>44</v>
       </c>
@@ -3565,7 +3565,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.6" customHeight="1">
-      <c r="B13" s="100"/>
+      <c r="B13" s="101"/>
       <c r="C13" s="39"/>
       <c r="D13" s="39" t="s">
         <v>45</v>
@@ -4654,7 +4654,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="99" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -4665,7 +4665,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="B11" s="99"/>
+      <c r="B11" s="100"/>
       <c r="D11" s="25" t="s">
         <v>43</v>
       </c>
@@ -4674,7 +4674,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B12" s="99"/>
+      <c r="B12" s="100"/>
       <c r="D12" s="33" t="s">
         <v>44</v>
       </c>
@@ -4683,7 +4683,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B13" s="100"/>
+      <c r="B13" s="101"/>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="40"/>
@@ -5768,7 +5768,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B10" s="101" t="s">
+      <c r="B10" s="102" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -5779,7 +5779,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B11" s="100"/>
+      <c r="B11" s="101"/>
       <c r="C11" s="54"/>
       <c r="D11" s="54"/>
       <c r="E11" s="55"/>
@@ -8170,7 +8170,7 @@
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
       <c r="A10" s="72"/>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="103" t="s">
         <v>81</v>
       </c>
       <c r="D10" s="69" t="s">
@@ -8182,7 +8182,7 @@
     </row>
     <row r="11" spans="1:5" ht="12.75" customHeight="1">
       <c r="A11" s="72"/>
-      <c r="B11" s="99"/>
+      <c r="B11" s="100"/>
       <c r="D11" s="25" t="s">
         <v>43</v>
       </c>
@@ -8192,7 +8192,7 @@
     </row>
     <row r="12" spans="1:5" ht="12.75" customHeight="1">
       <c r="A12" s="72"/>
-      <c r="B12" s="99"/>
+      <c r="B12" s="100"/>
       <c r="D12" s="25" t="s">
         <v>45</v>
       </c>
@@ -8202,7 +8202,7 @@
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
       <c r="A13" s="72"/>
-      <c r="B13" s="100"/>
+      <c r="B13" s="101"/>
       <c r="E13" s="75"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1">
@@ -8255,7 +8255,7 @@
     </row>
     <row r="18" spans="1:5" ht="16.5" customHeight="1">
       <c r="A18" s="72"/>
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="104" t="s">
         <v>87</v>
       </c>
       <c r="C18" s="77"/>
@@ -8268,7 +8268,7 @@
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="A19" s="72"/>
-      <c r="B19" s="104"/>
+      <c r="B19" s="105"/>
       <c r="C19" s="72"/>
       <c r="D19" s="25" t="s">
         <v>43</v>
@@ -8279,7 +8279,7 @@
     </row>
     <row r="20" spans="1:5" ht="33.75" customHeight="1">
       <c r="A20" s="72"/>
-      <c r="B20" s="104"/>
+      <c r="B20" s="105"/>
       <c r="C20" s="72"/>
       <c r="D20" s="54" t="s">
         <v>88</v>
@@ -8290,7 +8290,7 @@
     </row>
     <row r="21" spans="1:5" ht="18.600000000000001" customHeight="1">
       <c r="A21" s="44"/>
-      <c r="B21" s="105"/>
+      <c r="B21" s="106"/>
       <c r="C21" s="78"/>
       <c r="D21" s="25" t="s">
         <v>45</v>
@@ -9318,7 +9318,7 @@
         <v>22</v>
       </c>
       <c r="B3" s="84" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" s="85"/>
       <c r="D3" s="85"/>
@@ -9392,7 +9392,7 @@
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
       <c r="A10" s="72"/>
-      <c r="B10" s="106" t="s">
+      <c r="B10" s="107" t="s">
         <v>106</v>
       </c>
       <c r="C10" s="85"/>
@@ -9405,7 +9405,7 @@
     </row>
     <row r="11" spans="1:5" ht="12.75" customHeight="1">
       <c r="A11" s="72"/>
-      <c r="B11" s="107"/>
+      <c r="B11" s="108"/>
       <c r="C11" s="85"/>
       <c r="D11" s="33" t="s">
         <v>43</v>
@@ -9416,7 +9416,7 @@
     </row>
     <row r="12" spans="1:5" ht="12.75" customHeight="1">
       <c r="A12" s="72"/>
-      <c r="B12" s="107"/>
+      <c r="B12" s="108"/>
       <c r="C12" s="85"/>
       <c r="D12" s="33" t="s">
         <v>45</v>
@@ -9427,7 +9427,7 @@
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
       <c r="A13" s="72"/>
-      <c r="B13" s="108"/>
+      <c r="B13" s="109"/>
       <c r="C13" s="85"/>
       <c r="D13" s="85"/>
       <c r="E13" s="75"/>
@@ -9484,7 +9484,7 @@
     </row>
     <row r="18" spans="1:5" ht="12.75" customHeight="1">
       <c r="A18" s="72"/>
-      <c r="B18" s="106" t="s">
+      <c r="B18" s="107" t="s">
         <v>110</v>
       </c>
       <c r="C18" s="85"/>
@@ -9497,7 +9497,7 @@
     </row>
     <row r="19" spans="1:5" ht="12.75" customHeight="1">
       <c r="A19" s="72"/>
-      <c r="B19" s="107"/>
+      <c r="B19" s="108"/>
       <c r="C19" s="85"/>
       <c r="D19" s="33" t="s">
         <v>43</v>
@@ -9508,7 +9508,7 @@
     </row>
     <row r="20" spans="1:5" ht="12.75" customHeight="1">
       <c r="A20" s="72"/>
-      <c r="B20" s="107"/>
+      <c r="B20" s="108"/>
       <c r="C20" s="85"/>
       <c r="D20" s="33" t="s">
         <v>45</v>
@@ -9519,7 +9519,7 @@
     </row>
     <row r="21" spans="1:5" ht="12.75" customHeight="1">
       <c r="A21" s="72"/>
-      <c r="B21" s="108"/>
+      <c r="B21" s="109"/>
       <c r="C21" s="85"/>
       <c r="D21" s="85"/>
       <c r="E21" s="75"/>
@@ -9576,7 +9576,7 @@
     </row>
     <row r="26" spans="1:5" ht="12.75" customHeight="1">
       <c r="A26" s="72"/>
-      <c r="B26" s="106" t="s">
+      <c r="B26" s="107" t="s">
         <v>115</v>
       </c>
       <c r="C26" s="85"/>
@@ -9589,7 +9589,7 @@
     </row>
     <row r="27" spans="1:5" ht="12.75" customHeight="1">
       <c r="A27" s="72"/>
-      <c r="B27" s="107"/>
+      <c r="B27" s="108"/>
       <c r="C27" s="85"/>
       <c r="D27" s="33" t="s">
         <v>43</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="28" spans="1:5" ht="12.75" customHeight="1">
       <c r="A28" s="72"/>
-      <c r="B28" s="107"/>
+      <c r="B28" s="108"/>
       <c r="C28" s="85"/>
       <c r="D28" s="33" t="s">
         <v>45</v>
@@ -9611,7 +9611,7 @@
     </row>
     <row r="29" spans="1:5" ht="12.75" customHeight="1">
       <c r="A29" s="72"/>
-      <c r="B29" s="108"/>
+      <c r="B29" s="109"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
       <c r="E29" s="75"/>
@@ -9668,7 +9668,7 @@
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1">
       <c r="A34" s="72"/>
-      <c r="B34" s="106" t="s">
+      <c r="B34" s="107" t="s">
         <v>119</v>
       </c>
       <c r="C34" s="85"/>
@@ -9681,7 +9681,7 @@
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1">
       <c r="A35" s="72"/>
-      <c r="B35" s="107"/>
+      <c r="B35" s="108"/>
       <c r="C35" s="85"/>
       <c r="D35" s="33" t="s">
         <v>43</v>
@@ -9692,7 +9692,7 @@
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1">
       <c r="A36" s="72"/>
-      <c r="B36" s="107"/>
+      <c r="B36" s="108"/>
       <c r="C36" s="85"/>
       <c r="D36" s="33" t="s">
         <v>45</v>
@@ -9703,7 +9703,7 @@
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1">
       <c r="A37" s="72"/>
-      <c r="B37" s="108"/>
+      <c r="B37" s="109"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
       <c r="E37" s="75"/>
@@ -9760,8 +9760,8 @@
     </row>
     <row r="42" spans="1:5" ht="12.75" customHeight="1">
       <c r="A42" s="72"/>
-      <c r="B42" s="106" t="s">
-        <v>124</v>
+      <c r="B42" s="107" t="s">
+        <v>136</v>
       </c>
       <c r="C42" s="85"/>
       <c r="D42" s="69" t="s">
@@ -9773,7 +9773,7 @@
     </row>
     <row r="43" spans="1:5" ht="12.75" customHeight="1">
       <c r="A43" s="72"/>
-      <c r="B43" s="107"/>
+      <c r="B43" s="108"/>
       <c r="C43" s="85"/>
       <c r="D43" s="33" t="s">
         <v>43</v>
@@ -9784,7 +9784,7 @@
     </row>
     <row r="44" spans="1:5" ht="12.75" customHeight="1">
       <c r="A44" s="72"/>
-      <c r="B44" s="107"/>
+      <c r="B44" s="108"/>
       <c r="C44" s="85"/>
       <c r="D44" s="33" t="s">
         <v>45</v>
@@ -9795,18 +9795,18 @@
     </row>
     <row r="45" spans="1:5" ht="76.2" customHeight="1">
       <c r="A45" s="72"/>
-      <c r="B45" s="108"/>
+      <c r="B45" s="109"/>
       <c r="C45" s="85"/>
-      <c r="D45" s="109" t="s">
-        <v>129</v>
+      <c r="D45" s="98" t="s">
+        <v>128</v>
       </c>
       <c r="E45" s="97" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="12.75" customHeight="1">
       <c r="A46" s="86" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B46" s="76" t="s">
         <v>101</v>
@@ -9831,14 +9831,14 @@
     <row r="48" spans="1:5" ht="34.799999999999997" customHeight="1">
       <c r="A48" s="72"/>
       <c r="B48" s="93" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C48" s="85"/>
       <c r="D48" s="33" t="s">
         <v>79</v>
       </c>
       <c r="E48" s="92" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="12.75" customHeight="1">
@@ -9856,8 +9856,8 @@
     </row>
     <row r="50" spans="1:5" ht="12.75" customHeight="1">
       <c r="A50" s="72"/>
-      <c r="B50" s="106" t="s">
-        <v>128</v>
+      <c r="B50" s="107" t="s">
+        <v>127</v>
       </c>
       <c r="C50" s="85"/>
       <c r="D50" s="69" t="s">
@@ -9869,7 +9869,7 @@
     </row>
     <row r="51" spans="1:5" ht="12.75" customHeight="1">
       <c r="A51" s="72"/>
-      <c r="B51" s="107"/>
+      <c r="B51" s="108"/>
       <c r="C51" s="85"/>
       <c r="D51" s="33" t="s">
         <v>43</v>
@@ -9880,7 +9880,7 @@
     </row>
     <row r="52" spans="1:5" ht="12.75" customHeight="1">
       <c r="A52" s="72"/>
-      <c r="B52" s="107"/>
+      <c r="B52" s="108"/>
       <c r="C52" s="85"/>
       <c r="D52" s="33" t="s">
         <v>45</v>
@@ -9891,46 +9891,46 @@
     </row>
     <row r="53" spans="1:5" ht="73.2" customHeight="1">
       <c r="A53" s="72"/>
-      <c r="B53" s="107"/>
+      <c r="B53" s="108"/>
       <c r="C53" s="85"/>
       <c r="D53" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="E53" s="97" t="s">
         <v>129</v>
-      </c>
-      <c r="E53" s="97" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="44.4" customHeight="1">
       <c r="A54" s="85"/>
-      <c r="B54" s="107"/>
+      <c r="B54" s="108"/>
       <c r="C54" s="85"/>
       <c r="D54" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="97" t="s">
         <v>131</v>
-      </c>
-      <c r="E54" s="97" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="36" customHeight="1">
       <c r="A55" s="85"/>
-      <c r="B55" s="107"/>
+      <c r="B55" s="108"/>
       <c r="C55" s="85"/>
       <c r="D55" s="85" t="s">
         <v>43</v>
       </c>
       <c r="E55" s="97" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="24" customHeight="1">
       <c r="A56" s="85"/>
-      <c r="B56" s="108"/>
+      <c r="B56" s="109"/>
       <c r="C56" s="85"/>
       <c r="D56" s="85" t="s">
         <v>45</v>
       </c>
       <c r="E56" s="97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="12.75" customHeight="1"/>
@@ -10975,7 +10975,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="99" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="79"/>
@@ -10987,7 +10987,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="B11" s="99"/>
+      <c r="B11" s="100"/>
       <c r="C11" s="81"/>
       <c r="D11" s="25" t="s">
         <v>43</v>
@@ -10997,7 +10997,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.25" customHeight="1">
-      <c r="B12" s="100"/>
+      <c r="B12" s="101"/>
       <c r="C12" s="82"/>
       <c r="D12" s="39" t="s">
         <v>45</v>
@@ -11007,7 +11007,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="99" t="s">
         <v>96</v>
       </c>
       <c r="C13" s="79"/>
@@ -11015,12 +11015,12 @@
       <c r="E13" s="83"/>
     </row>
     <row r="14" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B14" s="99"/>
+      <c r="B14" s="100"/>
       <c r="C14" s="81"/>
       <c r="E14" s="34"/>
     </row>
     <row r="15" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B15" s="100"/>
+      <c r="B15" s="101"/>
       <c r="C15" s="82"/>
       <c r="D15" s="39"/>
       <c r="E15" s="40"/>
